--- a/Tables/Anthrone_complete.xlsx
+++ b/Tables/Anthrone_complete.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M339"/>
+  <dimension ref="A1:M341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -18020,40 +18020,40 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>121.2</t>
         </is>
       </c>
       <c r="B334">
-        <v>0.101</v>
+        <v>0.046</v>
       </c>
       <c r="C334">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D334">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>9_2</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>0.85378472222222201</t>
+          <t>0.93805555555555598</t>
         </is>
       </c>
       <c r="I334">
-        <v>0.051</v>
+        <v>-0.004000000000000004</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
@@ -18061,52 +18061,52 @@
         </is>
       </c>
       <c r="K334">
-        <v>2.288202425237107</v>
+        <v>-0.4944446603163766</v>
       </c>
       <c r="L334">
-        <v>0.300161111</v>
+        <v>0.0008611109999999977</v>
       </c>
       <c r="M334">
-        <v>7.623247454055122</v>
+        <v>-574.193873166616</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="B335">
-        <v>0.112</v>
+        <v>0.045</v>
       </c>
       <c r="C335">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D335">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>9_2</t>
+          <t>12_1</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>0.93805555555555598</t>
+          <t>5.115740740740741E-3</t>
         </is>
       </c>
       <c r="I335">
-        <v>0.062</v>
+        <v>-0.005000000000000004</v>
       </c>
       <c r="J335" t="inlineStr">
         <is>
@@ -18114,33 +18114,33 @@
         </is>
       </c>
       <c r="K335">
-        <v>2.844731842347803</v>
+        <v>-0.5450382436900763</v>
       </c>
       <c r="L335">
-        <v>0.224961111</v>
+        <v>0.002361110999999999</v>
       </c>
       <c r="M335">
-        <v>12.64543827020753</v>
+        <v>-230.839737602373</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>122.3</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="B336">
-        <v>0.075</v>
+        <v>0.101</v>
       </c>
       <c r="C336">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D336">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>11_4</t>
+          <t>6_1</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -18150,16 +18150,16 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>12:02:20 AM</t>
+          <t>0.85378472222222201</t>
         </is>
       </c>
       <c r="I336">
-        <v>0.02499999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
@@ -18167,52 +18167,52 @@
         </is>
       </c>
       <c r="K336">
-        <v>0.9727692575209144</v>
+        <v>2.288202425237107</v>
       </c>
       <c r="L336">
-        <v>0.318611111</v>
+        <v>0.300161111</v>
       </c>
       <c r="M336">
-        <v>3.05315547366744</v>
+        <v>7.623247454055122</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>123.1</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="B337">
-        <v>0.155</v>
+        <v>0.112</v>
       </c>
       <c r="C337">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D337">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>6_1</t>
+          <t>9_2</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>0.85378472222222201</t>
+          <t>0.93805555555555598</t>
         </is>
       </c>
       <c r="I337">
-        <v>0.105</v>
+        <v>0.062</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -18220,52 +18220,52 @@
         </is>
       </c>
       <c r="K337">
-        <v>5.02025592741689</v>
+        <v>2.844731842347803</v>
       </c>
       <c r="L337">
-        <v>0.404861111</v>
+        <v>0.224961111</v>
       </c>
       <c r="M337">
-        <v>12.39994603338647</v>
+        <v>12.64543827020753</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>122.3</t>
         </is>
       </c>
       <c r="B338">
-        <v>0.136</v>
+        <v>0.075</v>
       </c>
       <c r="C338">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D338">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>9_2</t>
+          <t>11_4</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>0.93805555555555598</t>
+          <t>12:02:20 AM</t>
         </is>
       </c>
       <c r="I338">
-        <v>0.08600000000000001</v>
+        <v>0.02499999999999999</v>
       </c>
       <c r="J338" t="inlineStr">
         <is>
@@ -18273,65 +18273,171 @@
         </is>
       </c>
       <c r="K338">
-        <v>4.058977843316597</v>
+        <v>0.9727692575209144</v>
       </c>
       <c r="L338">
-        <v>0.359511111</v>
+        <v>0.318611111</v>
       </c>
       <c r="M338">
-        <v>11.29027092382855</v>
+        <v>3.05315547366744</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
+          <t>123.1</t>
+        </is>
+      </c>
+      <c r="B339">
+        <v>0.155</v>
+      </c>
+      <c r="C339">
+        <v>1</v>
+      </c>
+      <c r="D339">
+        <v>6</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>6_1</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>0.85378472222222201</t>
+        </is>
+      </c>
+      <c r="I339">
+        <v>0.105</v>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>Dry</t>
+        </is>
+      </c>
+      <c r="K339">
+        <v>5.02025592741689</v>
+      </c>
+      <c r="L339">
+        <v>0.404861111</v>
+      </c>
+      <c r="M339">
+        <v>12.39994603338647</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>123.2</t>
+        </is>
+      </c>
+      <c r="B340">
+        <v>0.136</v>
+      </c>
+      <c r="C340">
+        <v>2</v>
+      </c>
+      <c r="D340">
+        <v>9</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>9_2</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>0.93805555555555598</t>
+        </is>
+      </c>
+      <c r="I340">
+        <v>0.08600000000000001</v>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>Dry</t>
+        </is>
+      </c>
+      <c r="K340">
+        <v>4.058977843316597</v>
+      </c>
+      <c r="L340">
+        <v>0.359511111</v>
+      </c>
+      <c r="M340">
+        <v>11.29027092382855</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
           <t>123.3</t>
         </is>
       </c>
-      <c r="B339">
+      <c r="B341">
         <v>0.074</v>
       </c>
-      <c r="C339">
+      <c r="C341">
         <v>4</v>
       </c>
-      <c r="D339">
+      <c r="D341">
         <v>11</v>
       </c>
-      <c r="E339" t="inlineStr">
+      <c r="E341" t="inlineStr">
         <is>
           <t>11_4</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr">
+      <c r="F341" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr">
+      <c r="G341" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr">
+      <c r="H341" t="inlineStr">
         <is>
           <t>12:02:20 AM</t>
         </is>
       </c>
-      <c r="I339">
+      <c r="I341">
         <v>0.02399999999999999</v>
       </c>
-      <c r="J339" t="inlineStr">
+      <c r="J341" t="inlineStr">
         <is>
           <t>Dry</t>
         </is>
       </c>
-      <c r="K339">
+      <c r="K341">
         <v>0.9221756741472147</v>
       </c>
-      <c r="L339">
+      <c r="L341">
         <v>0.365561111</v>
       </c>
-      <c r="M339">
+      <c r="M341">
         <v>2.522630680338464</v>
       </c>
     </row>
